--- a/Models/КРС/results/КРС - Лучшие модели.xlsx
+++ b/Models/КРС/results/КРС - Лучшие модели.xlsx
@@ -462,17 +462,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.77</v>
+        <v>5.59</v>
       </c>
       <c r="C2" t="n">
-        <v>5.22</v>
+        <v>4.67</v>
       </c>
       <c r="D2" t="n">
-        <v>11.16</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -483,13 +483,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.54</v>
+        <v>4.65</v>
       </c>
       <c r="C3" t="n">
-        <v>12.77</v>
+        <v>6.46</v>
       </c>
       <c r="D3" t="n">
-        <v>13.06</v>
+        <v>8.93</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -504,13 +504,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.93</v>
+        <v>10.36</v>
       </c>
       <c r="C4" t="n">
-        <v>11.63</v>
+        <v>5.71</v>
       </c>
       <c r="D4" t="n">
-        <v>29.88</v>
+        <v>15.36</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -525,17 +525,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.869999999999999</v>
+        <v>6.33</v>
       </c>
       <c r="C5" t="n">
-        <v>8.609999999999999</v>
+        <v>6.66</v>
       </c>
       <c r="D5" t="n">
-        <v>17.81</v>
+        <v>15.71</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.460000000000001</v>
+        <v>7.59</v>
       </c>
       <c r="C6" t="n">
-        <v>10.5</v>
+        <v>6.53</v>
       </c>
       <c r="D6" t="n">
-        <v>35.06</v>
+        <v>12.76</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -566,15 +566,11 @@
           <t>ГАЛМАТЫ</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>100.69</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>87.36</v>
-      </c>
-      <c r="D7" t="n">
-        <v>89.48</v>
-      </c>
+        <v>2.286066562543349e+22</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>SARIMA</t>
@@ -588,17 +584,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.6</v>
+        <v>13.02</v>
       </c>
       <c r="C8" t="n">
-        <v>26.88</v>
+        <v>11.14</v>
       </c>
       <c r="D8" t="n">
-        <v>26.3</v>
+        <v>16.69</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -609,17 +605,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43.1</v>
+        <v>35.63</v>
       </c>
       <c r="C9" t="n">
-        <v>28.85</v>
+        <v>37.61</v>
       </c>
       <c r="D9" t="n">
-        <v>46.33</v>
+        <v>33.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>Prophet</t>
         </is>
       </c>
     </row>
@@ -630,13 +626,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10.74</v>
+        <v>13.97</v>
       </c>
       <c r="C10" t="n">
-        <v>9.24</v>
+        <v>11.55</v>
       </c>
       <c r="D10" t="n">
-        <v>10.74</v>
+        <v>13.19</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -651,17 +647,17 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.22</v>
+        <v>4.54</v>
       </c>
       <c r="C11" t="n">
-        <v>4.57</v>
+        <v>4.25</v>
       </c>
       <c r="D11" t="n">
-        <v>5.69</v>
+        <v>4.02</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>Prophet</t>
         </is>
       </c>
     </row>
@@ -672,13 +668,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.67</v>
+        <v>3.69</v>
       </c>
       <c r="C12" t="n">
-        <v>8.470000000000001</v>
+        <v>5.62</v>
       </c>
       <c r="D12" t="n">
-        <v>22.68</v>
+        <v>14.75</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -693,17 +689,17 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14.93</v>
+        <v>12.74</v>
       </c>
       <c r="C13" t="n">
-        <v>18.38</v>
+        <v>11.68</v>
       </c>
       <c r="D13" t="n">
-        <v>20.16</v>
+        <v>9.93</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>Prophet</t>
         </is>
       </c>
     </row>
@@ -714,17 +710,17 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.31</v>
+        <v>8.25</v>
       </c>
       <c r="C14" t="n">
-        <v>5.56</v>
+        <v>12.39</v>
       </c>
       <c r="D14" t="n">
-        <v>6.77</v>
+        <v>9.06</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -735,17 +731,17 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.3</v>
+        <v>26.67</v>
       </c>
       <c r="C15" t="n">
-        <v>20.85</v>
+        <v>43.21</v>
       </c>
       <c r="D15" t="n">
-        <v>34.55</v>
+        <v>55.99</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -756,13 +752,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.42</v>
+        <v>13.01</v>
       </c>
       <c r="C16" t="n">
-        <v>50.75</v>
+        <v>13.21</v>
       </c>
       <c r="D16" t="n">
-        <v>37.86</v>
+        <v>32.95</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -777,13 +773,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28.17</v>
+        <v>14.94</v>
       </c>
       <c r="C17" t="n">
-        <v>73.61</v>
+        <v>30.85</v>
       </c>
       <c r="D17" t="n">
-        <v>62.62</v>
+        <v>31.17</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -798,17 +794,17 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20.29</v>
+        <v>23.12</v>
       </c>
       <c r="C18" t="n">
-        <v>78.15000000000001</v>
+        <v>17.24</v>
       </c>
       <c r="D18" t="n">
-        <v>94.19</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -819,13 +815,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.22</v>
+        <v>14.97</v>
       </c>
       <c r="C19" t="n">
-        <v>14.19</v>
+        <v>11.15</v>
       </c>
       <c r="D19" t="n">
-        <v>14.39</v>
+        <v>12.82</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -840,13 +836,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.93</v>
+        <v>6.26</v>
       </c>
       <c r="C20" t="n">
-        <v>8.23</v>
+        <v>5.99</v>
       </c>
       <c r="D20" t="n">
-        <v>11.59</v>
+        <v>13.73</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -861,13 +857,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.54</v>
+        <v>16.2</v>
       </c>
       <c r="C21" t="n">
-        <v>22.88</v>
+        <v>16.74</v>
       </c>
       <c r="D21" t="n">
-        <v>21.88</v>
+        <v>21.59</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
